--- a/saida_skus/SKU_UTD-001-AZ-VARAL-CABIDE-AZUL.xlsx
+++ b/saida_skus/SKU_UTD-001-AZ-VARAL-CABIDE-AZUL.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 102,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -598,24 +598,24 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▼ 26,7%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 31,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>13</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 102,00</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 34,8%</t>
+        <v>12</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 31,00</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>▼ 67,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 43,8%</t>
+        <v>16</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▲ 45,5%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 31,00</t>
+          <t>R$ 94,00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -963,16 +963,16 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>▼ 41,7%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 5,9%</t>
+        <v>11</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>▼ 26,7%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1103,17 +1103,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 7,7%</t>
+        <v>2</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1173,33 +1173,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 5,6%</t>
+        <v>15</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>▼ 34,8%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,33 +1246,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1319,33 +1319,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 135,00</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 98,5%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 5,9%</t>
+        <v>23</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▲ 43,8%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1392,25 +1392,25 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 31,00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 13,3%</t>
+        <v>7</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>▼ 41,7%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1474,24 +1474,24 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>▲ 240,0%</t>
+          <t>▼ 5,9%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 28,6%</t>
+        <v>12</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>▼ 7,7%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1614,17 +1614,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 58,3%</t>
+        <v>17</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▼ 5,6%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,33 +1684,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 144,00</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1757,25 +1757,25 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 135,00</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>▲ 98,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>▼ 7,7%</t>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1830,25 +1830,25 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 65,00</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 59,9%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,7%</t>
+        <v>13</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>▼ 13,3%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1903,29 +1903,29 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 18,2%</t>
+        <v>17</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▲ 240,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 162,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1989,20 +1989,20 @@
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>▲ 114,3%</t>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2049,33 +2049,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>▲ 10,0%</t>
+          <t>▼ 58,3%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2125,17 +2125,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>21</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2195,33 +2195,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 102,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 23,1%</t>
+        <v>12</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▼ 7,7%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2268,25 +2268,25 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 67,0%</t>
+          <t>R$ 65,00</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>▼ 59,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>14</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2341,33 +2341,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 102,00</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 62,5%</t>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▲ 18,2%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2414,33 +2414,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 97,00</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>▲ 203,1%</t>
+          <t>R$ 162,00</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>15</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▲ 114,3%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2487,33 +2487,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 43,3%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>▼ 42,9%</t>
+          <t>▲ 10,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2560,33 +2560,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 22,2%</t>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2633,33 +2633,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 60,00</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2709,22 +2709,22 @@
           <t>R$ 32,00</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>▼ 67,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
@@ -2749,12 +2749,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2779,33 +2779,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 180,00</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 31,6%</t>
+        <v>13</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2852,33 +2852,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>R$ 97,00</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,8%</t>
+          <t>▲ 203,1%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>▼ 9,1%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2895,12 +2895,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2925,33 +2925,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 210,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>▲ 600,0%</t>
+          <t>▼ 43,3%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>▲ 46,2%</t>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2968,12 +2968,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2998,33 +2998,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 65,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 8,3%</t>
+        <v>7</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>▼ 22,2%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3071,38 +3071,38 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 30,00</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,8%</t>
+          <t>R$ 60,00</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>14</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▼ 44,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -3114,12 +3114,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3144,33 +3144,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3217,33 +3217,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 180,00</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>25</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▲ 31,6%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3290,25 +3290,25 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 65,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>▲ 103,1%</t>
+          <t>▼ 50,8%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>10</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3333,12 +3333,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3363,33 +3363,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 210,00</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 46,2%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>R$ 65,00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3445,24 +3445,24 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>▼ 8,3%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3509,38 +3509,38 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
+          <t>R$ 30,00</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>▼ 11,8%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I42" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3585,17 +3585,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr">
+      <c r="H43" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>▲ 11,1%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3655,20 +3655,20 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3677,11 +3677,11 @@
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3728,25 +3728,25 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
+          <t>R$ 65,00</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>▲ 103,1%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 30,8%</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
@@ -3754,7 +3754,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3801,25 +3801,25 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3883,11 +3883,11 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>▲ 8,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3896,11 +3896,11 @@
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3947,33 +3947,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 59,8%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 46,7%</t>
+        <v>15</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3990,12 +3990,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4023,17 +4023,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr">
+      <c r="H49" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4063,12 +4063,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4093,33 +4093,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 169,00</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 9,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 83,4%</t>
+        <v>0</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4166,25 +4166,25 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H51" s="4" t="inlineStr">
-        <is>
-          <t>▲ 5,9%</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>▲ 11,1%</t>
+          <t>▼ 30,8%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4239,33 +4239,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 186,00</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>▲ 481,2%</t>
+          <t>R$ 102,00</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>181</v>
+        <v>12</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>▲ 546,4%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4321,24 +4321,24 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,2%</t>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4385,33 +4385,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>▼ 59,8%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>▲ 47,4%</t>
+          <t>▼ 46,7%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4461,17 +4461,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>▼ 21,4%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4531,38 +4531,38 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 169,00</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>30</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>▼ 83,4%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
@@ -4574,12 +4574,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4604,33 +4604,33 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>▲ 7,7%</t>
+        <v>10</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4677,33 +4677,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
+          <t>R$ 186,00</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,6%</t>
+          <t>▲ 481,2%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 546,4%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4720,12 +4720,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4750,33 +4750,33 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>▲ 62,5%</t>
+          <t>▼ 18,2%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4793,12 +4793,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4823,33 +4823,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 129,00</t>
-        </is>
-      </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1,6%</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,2%</t>
+          <t>▲ 47,4%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4896,33 +4896,33 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
-        </is>
-      </c>
-      <c r="H61" s="4" t="inlineStr">
-        <is>
-          <t>▲ 63,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>▼ 21,4%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4969,38 +4969,38 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 127,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>▲ 296,9%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 5,9%</t>
+        <v>19</v>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
@@ -5012,12 +5012,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5042,33 +5042,33 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 65,00</t>
-        </is>
-      </c>
-      <c r="H63" s="4" t="inlineStr">
-        <is>
-          <t>▲ 103,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>▼ 9,1%</t>
+          <t>▲ 7,7%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5115,33 +5115,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 83,2%</t>
+          <t>R$ 96,00</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,6%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 32,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5188,33 +5188,33 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>13</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5261,33 +5261,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 191,00</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 99,0%</t>
+          <t>R$ 129,00</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>▲ 1,6%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>▲ 47,1%</t>
+          <t>▼ 6,2%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5304,12 +5304,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5334,33 +5334,33 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>▲ 63,1%</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>▲ 450,0%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5377,12 +5377,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5407,25 +5407,25 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 127,00</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>▲ 296,9%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 32,0%</t>
+        <v>16</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>▼ 5,9%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
@@ -5433,7 +5433,7 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5450,12 +5450,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5480,25 +5480,25 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 65,00</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>▲ 103,1%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5553,38 +5553,38 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>▼ 83,2%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 86,3%</t>
+        <v>17</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▼ 32,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5631,20 +5631,20 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
@@ -5669,12 +5669,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5699,33 +5699,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 191,00</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>▲ 99,0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>182</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1416,7%</t>
+        <v>25</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▲ 47,1%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5742,12 +5742,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5772,33 +5772,33 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 450,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5845,33 +5845,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 96,00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>17</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▼ 32,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5923,20 +5923,20 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>▲ 233,3%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
@@ -5961,12 +5961,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 96,00</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -6000,29 +6000,29 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>25</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▼ 86,3%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
@@ -6034,78 +6034,516 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>4468602739</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>1854624004</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 33,87</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>182</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▲ 1416,7%</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>4468602739</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>1854624004</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 33,87</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>4468602739</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▲ 233,3%</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>UTD-001-AZ</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>Varal Cabide Azul</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>1854624004</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 33,87</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>4468602739</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>R$ 35,90</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="n">
+      <c r="I83" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J77" s="2" t="inlineStr">
+      <c r="J83" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K77" s="2" t="inlineStr">
+      <c r="K83" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="L77" s="2" t="n">
+      <c r="L83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M77" s="2" t="inlineStr">
+      <c r="M83" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="N77" s="2" t="inlineStr">
+      <c r="N83" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O77" s="2" t="inlineStr">
+      <c r="O83" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O77"/>
+  <autoFilter ref="A1:O83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-001-AZ-VARAL-CABIDE-AZUL.xlsx
+++ b/saida_skus/SKU_UTD-001-AZ-VARAL-CABIDE-AZUL.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O83"/>
+  <dimension ref="A1:O85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 135,00</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>▲ 32,4%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 31,00</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>▲ 119,4%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▲ 62,5%</t>
+        <v>5</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>▼ 61,5%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -738,22 +738,22 @@
           <t>R$ 102,00</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>▲ 50,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
@@ -761,7 +761,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -811,22 +811,22 @@
           <t>R$ 31,00</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>▼ 67,0%</t>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>13</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
@@ -834,7 +834,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -881,25 +881,25 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 102,00</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▲ 45,5%</t>
+        <v>12</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
@@ -907,7 +907,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -954,20 +954,20 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 94,00</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 31,00</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>▼ 67,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,14 +997,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -1027,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▼ 26,7%</t>
+        <v>16</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▲ 45,5%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,14 +1070,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 94,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1109,24 +1109,24 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>8</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,14 +1143,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -1178,20 +1178,20 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>▼ 34,8%</t>
+          <t>▼ 26,7%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,14 +1216,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -1249,17 +1249,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1289,14 +1289,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1328,24 +1328,24 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▲ 43,8%</t>
+        <v>15</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▼ 34,8%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,14 +1362,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -1392,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 31,00</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>▼ 41,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,14 +1435,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -1474,11 +1474,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▼ 5,9%</t>
+        <v>23</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▲ 43,8%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1508,14 +1508,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 31,00</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>▼ 7,7%</t>
+          <t>▼ 41,7%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,14 +1581,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -1614,17 +1614,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>▼ 5,6%</t>
+          <t>▼ 5,9%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1654,14 +1654,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -1684,33 +1684,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>12</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>▼ 7,7%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,14 +1727,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -1757,33 +1757,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 135,00</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>▲ 98,5%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▲ 5,9%</t>
+        <v>17</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>▼ 5,6%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,14 +1800,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -1830,33 +1830,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>▼ 13,3%</t>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,14 +1873,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -1903,33 +1903,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 135,00</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>▲ 98,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>▲ 240,0%</t>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,14 +1946,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -1981,20 +1981,20 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>▼ 28,6%</t>
+          <t>▼ 13,3%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
@@ -2019,14 +2019,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -2049,33 +2049,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▼ 58,3%</t>
+        <v>17</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▲ 240,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,14 +2092,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -2122,33 +2122,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>15</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,14 +2165,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -2195,33 +2195,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>▼ 7,7%</t>
+          <t>▼ 58,3%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,14 +2238,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -2268,33 +2268,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 65,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>▼ 59,9%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>▼ 6,7%</t>
+        <v>21</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,14 +2311,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -2344,22 +2344,22 @@
           <t>R$ 102,00</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▲ 18,2%</t>
+        <v>12</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▼ 7,7%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,14 +2384,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -2414,33 +2414,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 162,00</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 65,00</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>▼ 59,9%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▲ 114,3%</t>
+        <v>14</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,14 +2457,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -2487,33 +2487,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 102,00</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>▲ 10,0%</t>
+          <t>▲ 18,2%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2530,14 +2530,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -2560,33 +2560,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 162,00</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>15</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▲ 114,3%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,14 +2603,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2642,24 +2642,24 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▼ 23,1%</t>
+        <v>11</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▲ 10,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2676,14 +2676,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -2706,33 +2706,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>▼ 67,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="M31" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2749,14 +2749,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -2782,17 +2782,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▲ 62,5%</t>
+        <v>10</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2822,14 +2822,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -2852,33 +2852,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 97,00</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>▲ 203,1%</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>▼ 67,0%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2895,14 +2895,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -2925,33 +2925,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>▼ 43,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+        <v>13</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2968,14 +2968,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -2998,33 +2998,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 97,00</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>▲ 203,1%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>▼ 22,2%</t>
+        <v>14</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,14 +3041,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -3071,33 +3071,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 60,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 43,3%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>▼ 44,0%</t>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3114,14 +3114,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -3153,16 +3153,16 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>▼ 10,0%</t>
+          <t>▼ 22,2%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3187,14 +3187,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -3217,33 +3217,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 180,00</t>
+          <t>R$ 60,00</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▲ 31,6%</t>
+        <v>14</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▼ 44,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3260,14 +3260,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -3293,22 +3293,22 @@
           <t>R$ 32,00</t>
         </is>
       </c>
-      <c r="H39" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,8%</t>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>▼ 9,1%</t>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
@@ -3333,14 +3333,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -3363,33 +3363,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 210,00</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+          <t>R$ 180,00</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>▲ 46,2%</t>
+          <t>▲ 31,6%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3406,14 +3406,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -3436,33 +3436,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 65,00</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,8%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>▼ 8,3%</t>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,14 +3479,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -3509,38 +3509,38 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 30,00</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>▼ 11,8%</t>
+          <t>R$ 210,00</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>19</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▲ 46,2%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -3552,14 +3552,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -3582,33 +3582,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 65,00</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 8,3%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3625,14 +3625,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -3655,16 +3655,16 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 30,00</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>▼ 11,8%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -3698,14 +3698,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -3728,33 +3728,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 65,00</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>▲ 103,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>12</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3771,14 +3771,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -3806,15 +3806,15 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3844,14 +3844,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -3874,25 +3874,25 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
+          <t>R$ 65,00</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>▲ 103,1%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3917,14 +3917,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3956,11 +3956,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3969,11 +3969,11 @@
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3990,14 +3990,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -4020,33 +4020,33 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H49" s="4" t="inlineStr">
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I49" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>▲ 11,1%</t>
-        </is>
-      </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4063,14 +4063,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -4096,17 +4096,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>15</v>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4136,14 +4136,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -4166,33 +4166,33 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>▼ 30,8%</t>
+        <v>10</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4209,14 +4209,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -4239,33 +4239,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4282,14 +4282,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4321,24 +4321,24 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>▲ 8,3%</t>
+        <v>9</v>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>▼ 30,8%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4355,14 +4355,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -4385,33 +4385,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>▼ 59,8%</t>
+          <t>R$ 102,00</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>▼ 46,7%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4428,14 +4428,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -4461,17 +4461,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H55" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>▲ 20,0%</t>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4501,14 +4501,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -4531,33 +4531,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 169,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>▼ 9,1%</t>
+          <t>▼ 59,8%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>▼ 83,4%</t>
+          <t>▼ 46,7%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4574,14 +4574,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -4604,33 +4604,33 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>▲ 5,9%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>▲ 11,1%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4647,14 +4647,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -4677,33 +4677,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 186,00</t>
-        </is>
-      </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>▲ 481,2%</t>
+          <t>R$ 169,00</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>181</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▲ 546,4%</t>
+        <v>30</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▼ 83,4%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4720,14 +4720,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -4750,33 +4750,33 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>▼ 18,2%</t>
+        <v>10</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4793,14 +4793,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -4823,33 +4823,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 186,00</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>▲ 481,2%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>28</v>
+        <v>181</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>▲ 47,4%</t>
+          <t>▲ 546,4%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4866,14 +4866,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4905,24 +4905,24 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>▼ 21,4%</t>
+          <t>▼ 18,2%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4939,14 +4939,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -4969,38 +4969,38 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>28</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▲ 47,4%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
@@ -5012,14 +5012,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -5051,11 +5051,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▲ 7,7%</t>
+        <v>11</v>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>▼ 21,4%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5085,14 +5085,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -5115,38 +5115,38 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>▼ 25,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
+      <c r="M64" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="L64" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="M64" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
@@ -5158,14 +5158,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -5191,17 +5191,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H65" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>▲ 62,5%</t>
+          <t>▲ 7,7%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5231,14 +5231,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -5261,33 +5261,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 129,00</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>▲ 1,6%</t>
+          <t>R$ 96,00</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,6%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>▼ 6,2%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5304,14 +5304,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -5334,33 +5334,33 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
-        </is>
-      </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>▲ 63,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5377,14 +5377,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -5407,33 +5407,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 127,00</t>
+          <t>R$ 129,00</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>▲ 296,9%</t>
+          <t>▲ 1,6%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>▼ 5,9%</t>
+          <t>▼ 6,2%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5450,14 +5450,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -5480,33 +5480,33 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 65,00</t>
+          <t>R$ 106,00</t>
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>▲ 103,1%</t>
+          <t>▲ 63,1%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>▼ 9,1%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5523,14 +5523,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -5553,33 +5553,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>▼ 83,2%</t>
+          <t>R$ 127,00</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>▲ 296,9%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>▼ 32,0%</t>
+          <t>▼ 5,9%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5596,14 +5596,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -5626,25 +5626,25 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 65,00</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>▲ 103,1%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>10</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5669,14 +5669,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -5699,33 +5699,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 191,00</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>▲ 99,0%</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>▼ 83,2%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▲ 47,1%</t>
+        <v>17</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▼ 32,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5742,12 +5742,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5783,9 +5783,9 @@
       <c r="I73" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▲ 450,0%</t>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5815,14 +5815,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -5845,33 +5845,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 191,00</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>▲ 99,0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▼ 32,0%</t>
+        <v>25</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▲ 47,1%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5888,14 +5888,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -5927,16 +5927,16 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>▲ 450,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
@@ -5961,14 +5961,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -5996,20 +5996,20 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>▼ 86,3%</t>
+          <t>▼ 32,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
@@ -6034,14 +6034,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -6069,20 +6069,20 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
@@ -6090,7 +6090,7 @@
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6107,14 +6107,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -6137,7 +6137,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 96,00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6146,29 +6146,29 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>182</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▲ 1416,7%</t>
+        <v>25</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▼ 86,3%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
@@ -6180,14 +6180,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -6210,33 +6210,33 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H79" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6253,14 +6253,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -6292,11 +6292,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>182</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▲ 1416,7%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6326,14 +6326,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -6356,33 +6356,33 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>▲ 233,3%</t>
+        <v>5</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6399,14 +6399,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -6438,11 +6438,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>12</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6472,78 +6472,224 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>4468602739</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▲ 233,3%</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>UTD-001-AZ</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>Varal Cabide Azul</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>1854624004</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 33,87</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>4468602739</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>R$ 35,90</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="n">
+      <c r="I85" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J83" s="2" t="inlineStr">
+      <c r="J85" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K83" s="2" t="inlineStr">
+      <c r="K85" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="L83" s="2" t="n">
+      <c r="L85" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M83" s="2" t="inlineStr">
+      <c r="M85" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="N83" s="2" t="inlineStr">
+      <c r="N85" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O83" s="2" t="inlineStr">
+      <c r="O85" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O83"/>
+  <autoFilter ref="A1:O85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-001-AZ-VARAL-CABIDE-AZUL.xlsx
+++ b/saida_skus/SKU_UTD-001-AZ-VARAL-CABIDE-AZUL.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O85"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 135,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>▲ 32,4%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>22</v>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>▲ 69,2%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>▲ 119,4%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>▼ 61,5%</t>
+          <t>▲ 81,8%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,25 +735,25 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 169,00</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>▲ 65,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 7,1%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
@@ -761,7 +761,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,25 +808,25 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 31,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▲ 62,5%</t>
+        <v>11</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>▲ 10,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
@@ -834,7 +834,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -886,20 +886,20 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 24,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>14</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 22,2%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
@@ -907,7 +907,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,33 +954,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 31,00</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>▼ 67,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>10</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 135,00</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 32,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▲ 45,5%</t>
+        <v>18</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,33 +1100,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 94,00</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>▲ 119,4%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▼ 61,5%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 102,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1182,24 +1182,24 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>▼ 26,7%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,33 +1246,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 31,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>13</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1319,33 +1319,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 102,00</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▼ 34,8%</t>
+        <v>12</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1392,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 31,00</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 67,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1465,33 +1465,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▲ 43,8%</t>
+        <v>16</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 45,5%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 31,00</t>
+          <t>R$ 94,00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1547,16 +1547,16 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>▼ 41,7%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1611,33 +1611,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▼ 5,9%</t>
+        <v>11</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 26,7%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1687,17 +1687,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>▼ 7,7%</t>
+        <v>2</v>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1757,33 +1757,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▼ 5,6%</t>
+        <v>15</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 34,8%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1830,33 +1830,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1903,33 +1903,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 135,00</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>▲ 98,5%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▲ 5,9%</t>
+        <v>23</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 43,8%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1976,25 +1976,25 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 31,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>▼ 13,3%</t>
+        <v>7</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 41,7%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2058,24 +2058,24 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>▲ 240,0%</t>
+          <t>▼ 5,9%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2122,33 +2122,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>▼ 28,6%</t>
+        <v>12</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,7%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2198,17 +2198,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▼ 58,3%</t>
+        <v>17</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,6%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2268,33 +2268,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 144,00</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2341,25 +2341,25 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 135,00</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 98,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>▼ 7,7%</t>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2414,25 +2414,25 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 65,00</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>▼ 59,9%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>▼ 6,7%</t>
+        <v>13</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 13,3%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2487,29 +2487,29 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▲ 18,2%</t>
+        <v>17</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 240,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
@@ -2530,12 +2530,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 162,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2573,20 +2573,20 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>▲ 114,3%</t>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2633,33 +2633,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>▲ 10,0%</t>
+          <t>▼ 58,3%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2709,17 +2709,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>21</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2779,33 +2779,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 102,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▼ 23,1%</t>
+        <v>12</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,7%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2852,25 +2852,25 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>▼ 67,0%</t>
+          <t>R$ 65,00</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 59,9%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>14</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2895,12 +2895,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2925,33 +2925,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 102,00</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▲ 62,5%</t>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 18,2%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2968,12 +2968,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2998,33 +2998,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 97,00</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>▲ 203,1%</t>
+          <t>R$ 162,00</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>15</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>▲ 114,3%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3071,33 +3071,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>▼ 43,3%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>▼ 42,9%</t>
+          <t>▲ 10,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3114,12 +3114,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3144,33 +3144,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>▼ 22,2%</t>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3217,33 +3217,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 60,00</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▼ 44,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3293,22 +3293,22 @@
           <t>R$ 32,00</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 67,0%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>▼ 10,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
@@ -3333,12 +3333,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3363,33 +3363,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 180,00</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▲ 31,6%</t>
+        <v>13</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3436,33 +3436,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>R$ 97,00</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,8%</t>
+          <t>▲ 203,1%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>▼ 9,1%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3509,33 +3509,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 210,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>▲ 600,0%</t>
+          <t>▼ 43,3%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>▲ 46,2%</t>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3582,33 +3582,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 65,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>▼ 8,3%</t>
+        <v>7</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 22,2%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3655,38 +3655,38 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 30,00</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>▼ 11,8%</t>
+          <t>R$ 60,00</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>14</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3728,33 +3728,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H45" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3801,33 +3801,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 180,00</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>25</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▲ 31,6%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3874,25 +3874,25 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 65,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>▲ 103,1%</t>
+          <t>▼ 50,8%</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>10</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3947,33 +3947,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 210,00</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 46,2%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3990,12 +3990,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>R$ 65,00</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4029,24 +4029,24 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,3%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4063,12 +4063,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4093,38 +4093,38 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
+          <t>R$ 30,00</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,8%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4169,17 +4169,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H51" s="4" t="inlineStr">
+      <c r="H51" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>▲ 11,1%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4239,20 +4239,20 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4261,11 +4261,11 @@
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4312,25 +4312,25 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
+          <t>R$ 65,00</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>▲ 103,1%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>▼ 30,8%</t>
-        </is>
-      </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4385,25 +4385,25 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4467,11 +4467,11 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>▲ 8,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4480,11 +4480,11 @@
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4531,33 +4531,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr">
-        <is>
-          <t>▼ 59,8%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▼ 46,7%</t>
+        <v>15</v>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4574,12 +4574,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4607,17 +4607,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H57" s="4" t="inlineStr">
+      <c r="H57" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4677,33 +4677,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 169,00</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>▼ 9,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▼ 83,4%</t>
+        <v>0</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4720,12 +4720,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4750,25 +4750,25 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>▲ 5,9%</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>▲ 11,1%</t>
+          <t>▼ 30,8%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4793,12 +4793,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4823,33 +4823,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 186,00</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>▲ 481,2%</t>
+          <t>R$ 102,00</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>181</v>
+        <v>12</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>▲ 546,4%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4905,24 +4905,24 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>▼ 18,2%</t>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4969,33 +4969,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 59,8%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>▲ 47,4%</t>
+          <t>▼ 46,7%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5012,12 +5012,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5045,17 +5045,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>▼ 21,4%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5115,38 +5115,38 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 169,00</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>30</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 83,4%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5188,33 +5188,33 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▲ 7,7%</t>
+        <v>10</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5261,33 +5261,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
+          <t>R$ 186,00</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>▼ 25,6%</t>
+          <t>▲ 481,2%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>0</v>
+        <v>181</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 546,4%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5304,12 +5304,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5334,33 +5334,33 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H67" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>▲ 62,5%</t>
+          <t>▼ 18,2%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5377,12 +5377,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5407,33 +5407,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 129,00</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>▲ 1,6%</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>▼ 6,2%</t>
+          <t>▲ 47,4%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5450,12 +5450,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5480,33 +5480,33 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
-        </is>
-      </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>▲ 63,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,4%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5553,38 +5553,38 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 127,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>▲ 296,9%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▼ 5,9%</t>
+        <v>19</v>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5626,33 +5626,33 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 65,00</t>
-        </is>
-      </c>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t>▲ 103,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>▼ 9,1%</t>
+          <t>▲ 7,7%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5699,33 +5699,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>▼ 83,2%</t>
+          <t>R$ 96,00</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,6%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▼ 32,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5742,12 +5742,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5772,33 +5772,33 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>13</v>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5845,33 +5845,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 191,00</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>▲ 99,0%</t>
+          <t>R$ 129,00</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1,6%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>▲ 47,1%</t>
+          <t>▼ 6,2%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5918,33 +5918,33 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>▲ 63,1%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>▲ 450,0%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5961,12 +5961,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5991,25 +5991,25 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 127,00</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 296,9%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>▼ 32,0%</t>
+        <v>16</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,9%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6064,25 +6064,25 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 65,00</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>▲ 103,1%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
@@ -6090,7 +6090,7 @@
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6107,12 +6107,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6137,38 +6137,38 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 83,2%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▼ 86,3%</t>
+        <v>17</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 32,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6215,20 +6215,20 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
@@ -6253,12 +6253,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6283,33 +6283,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 191,00</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 99,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>182</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▲ 1416,7%</t>
+        <v>25</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 47,1%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6326,12 +6326,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6356,33 +6356,33 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H81" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 450,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6399,12 +6399,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6429,33 +6429,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 96,00</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>17</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 32,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6507,20 +6507,20 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>▲ 233,3%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
@@ -6545,12 +6545,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6575,7 +6575,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 96,00</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -6584,29 +6584,29 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>25</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 86,3%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
@@ -6618,78 +6618,516 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>4468602739</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>1854624004</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 33,87</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>182</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1416,7%</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>4468602739</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>1854624004</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 33,87</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>4468602739</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>▲ 233,3%</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>UTD-001-AZ</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>Varal Cabide Azul</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>1854624004</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 33,87</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>4468602739</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>R$ 35,90</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I85" s="2" t="n">
+      <c r="I91" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J85" s="2" t="inlineStr">
+      <c r="J91" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K85" s="2" t="inlineStr">
+      <c r="K91" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="L85" s="2" t="n">
+      <c r="L91" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M85" s="2" t="inlineStr">
+      <c r="M91" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="N85" s="2" t="inlineStr">
+      <c r="N91" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O85" s="2" t="inlineStr">
+      <c r="O91" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O85"/>
+  <autoFilter ref="A1:O91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-001-AZ-VARAL-CABIDE-AZUL.xlsx
+++ b/saida_skus/SKU_UTD-001-AZ-VARAL-CABIDE-AZUL.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:O97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>▲ 69,2%</t>
+        <v>23</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>▲ 81,8%</t>
+        <v>21</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 169,00</t>
+          <t>R$ 237,00</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>▲ 65,7%</t>
+          <t>▲ 132,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>▼ 7,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 203,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -817,24 +817,24 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>▲ 10,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -884,17 +884,17 @@
           <t>R$ 102,00</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 24,4%</t>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>▼ 22,2%</t>
+          <t>▼ 4,5%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -903,11 +903,11 @@
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -963,11 +963,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>17</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 135,00</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>▲ 32,4%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>22</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 69,2%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,33 +1100,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>▲ 119,4%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 61,5%</t>
+        <v>20</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>▲ 81,8%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1173,25 +1173,25 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 169,00</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>▲ 65,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,1%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,25 +1246,25 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 31,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>▲ 62,5%</t>
+          <t>▲ 10,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1322,22 +1322,22 @@
           <t>R$ 102,00</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 22,2%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1392,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 31,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>▼ 67,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>10</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1465,33 +1465,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 135,00</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 32,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 45,5%</t>
+        <v>18</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 94,00</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>▲ 119,4%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 61,5%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 102,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1620,24 +1620,24 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 26,7%</t>
+        <v>18</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,33 +1684,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 31,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>13</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1757,33 +1757,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 102,00</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>▼ 34,8%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1830,33 +1830,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 31,00</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 67,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1903,33 +1903,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>▲ 43,8%</t>
+          <t>▲ 45,5%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 31,00</t>
+          <t>R$ 94,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1985,16 +1985,16 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 41,7%</t>
+        <v>8</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2049,33 +2049,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>▼ 5,9%</t>
+          <t>▼ 26,7%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2125,17 +2125,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 7,7%</t>
+        <v>2</v>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2195,33 +2195,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>▼ 5,6%</t>
+          <t>▼ 34,8%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2268,33 +2268,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2341,33 +2341,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 135,00</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 98,5%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>▲ 5,9%</t>
+          <t>▲ 43,8%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2414,25 +2414,25 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 31,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>▼ 13,3%</t>
+          <t>▼ 41,7%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2496,24 +2496,24 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 240,0%</t>
+        <v>16</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,9%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2560,33 +2560,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>▼ 28,6%</t>
+          <t>▼ 7,7%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2642,11 +2642,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>▼ 58,3%</t>
+          <t>▼ 5,6%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2706,33 +2706,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2779,25 +2779,25 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 135,00</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 98,5%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 7,7%</t>
+        <v>18</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2852,25 +2852,25 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 65,00</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 59,9%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,7%</t>
+          <t>▼ 13,3%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2895,12 +2895,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2925,29 +2925,29 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>▲ 18,2%</t>
+          <t>▲ 240,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
@@ -2968,12 +2968,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 162,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3009,22 +3009,22 @@
       <c r="I35" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>▲ 114,3%</t>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3071,33 +3071,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▲ 10,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 58,3%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3114,12 +3114,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3153,11 +3153,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>21</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3217,33 +3217,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 102,00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,1%</t>
+          <t>▼ 7,7%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3290,25 +3290,25 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>R$ 65,00</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>▼ 67,0%</t>
+          <t>▼ 59,9%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3333,12 +3333,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 102,00</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
@@ -3376,20 +3376,20 @@
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>▲ 62,5%</t>
+          <t>▲ 18,2%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3436,33 +3436,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 97,00</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>▲ 203,1%</t>
+          <t>R$ 162,00</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 114,3%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3509,33 +3509,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 43,3%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+        <v>11</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 10,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3582,33 +3582,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 22,2%</t>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3655,33 +3655,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 60,00</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>▼ 44,0%</t>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3731,22 +3731,22 @@
           <t>R$ 32,00</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 67,0%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>▼ 10,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
@@ -3771,12 +3771,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3801,33 +3801,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 180,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>▲ 31,6%</t>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3874,33 +3874,33 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,8%</t>
+          <t>R$ 97,00</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>▲ 203,1%</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▼ 9,1%</t>
+        <v>14</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3947,33 +3947,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 210,00</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 43,3%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>▲ 46,2%</t>
+        <v>8</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3990,12 +3990,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4020,33 +4020,33 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 65,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>▼ 8,3%</t>
+          <t>▼ 22,2%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4063,12 +4063,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4093,38 +4093,38 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 30,00</t>
+          <t>R$ 60,00</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>▼ 11,8%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>14</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4166,33 +4166,33 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4239,33 +4239,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 180,00</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>25</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>▲ 31,6%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4312,25 +4312,25 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 65,00</t>
-        </is>
-      </c>
-      <c r="H53" s="4" t="inlineStr">
-        <is>
-          <t>▲ 103,1%</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,8%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>10</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4385,33 +4385,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 210,00</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>19</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▲ 46,2%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>R$ 65,00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4467,24 +4467,24 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 8,3%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4531,38 +4531,38 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
+          <t>R$ 30,00</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,8%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I56" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
@@ -4574,12 +4574,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4613,11 +4613,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>▲ 11,1%</t>
+        <v>12</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4677,20 +4677,20 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4699,11 +4699,11 @@
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4720,12 +4720,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4750,25 +4750,25 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
+          <t>R$ 65,00</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>▲ 103,1%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 30,8%</t>
-        </is>
-      </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4793,12 +4793,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4823,25 +4823,25 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
-        </is>
-      </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4905,11 +4905,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t>▲ 8,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4918,11 +4918,11 @@
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4969,33 +4969,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 59,8%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 46,7%</t>
+        <v>15</v>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5012,12 +5012,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5051,11 +5051,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>▲ 20,0%</t>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5115,33 +5115,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 169,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>▼ 9,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>▼ 83,4%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5188,25 +5188,25 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H65" s="4" t="inlineStr">
-        <is>
-          <t>▲ 5,9%</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>▲ 11,1%</t>
+        <v>9</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 30,8%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5261,33 +5261,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 186,00</t>
+          <t>R$ 102,00</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>▲ 481,2%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>181</v>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 546,4%</t>
+        <v>12</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5304,12 +5304,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5343,24 +5343,24 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 18,2%</t>
+        <v>13</v>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5377,12 +5377,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5407,33 +5407,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 59,8%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 47,4%</t>
+        <v>16</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 46,7%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5450,12 +5450,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5483,17 +5483,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 21,4%</t>
+        <v>12</v>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5553,38 +5553,38 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 169,00</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>30</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 83,4%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5626,33 +5626,33 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>▲ 7,7%</t>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5699,33 +5699,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,6%</t>
+          <t>R$ 186,00</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 481,2%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>181</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 546,4%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5742,12 +5742,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5772,33 +5772,33 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>▲ 62,5%</t>
+        <v>9</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,2%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5845,33 +5845,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 129,00</t>
-        </is>
-      </c>
-      <c r="H74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1,6%</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,2%</t>
+        <v>28</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 47,4%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5918,33 +5918,33 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
-        </is>
-      </c>
-      <c r="H75" s="4" t="inlineStr">
-        <is>
-          <t>▲ 63,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 21,4%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5961,12 +5961,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5991,38 +5991,38 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 127,00</t>
-        </is>
-      </c>
-      <c r="H76" s="4" t="inlineStr">
-        <is>
-          <t>▲ 296,9%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 5,9%</t>
+        <v>19</v>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6064,33 +6064,33 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 65,00</t>
-        </is>
-      </c>
-      <c r="H77" s="4" t="inlineStr">
-        <is>
-          <t>▲ 103,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 9,1%</t>
+        <v>14</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>▲ 7,7%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6107,12 +6107,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6137,33 +6137,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>R$ 96,00</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>▼ 83,2%</t>
+          <t>▼ 25,6%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>▼ 32,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6210,33 +6210,33 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>13</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6253,12 +6253,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6283,33 +6283,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 191,00</t>
+          <t>R$ 129,00</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>▲ 99,0%</t>
+          <t>▲ 1,6%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 47,1%</t>
+        <v>15</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,2%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6326,12 +6326,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6356,33 +6356,33 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>▲ 63,1%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>▲ 450,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6399,12 +6399,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6429,25 +6429,25 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 127,00</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 296,9%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>▼ 32,0%</t>
+          <t>▼ 5,9%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
@@ -6455,7 +6455,7 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6502,25 +6502,25 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 65,00</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>▲ 103,1%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6545,12 +6545,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6575,38 +6575,38 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 83,2%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>▼ 86,3%</t>
+          <t>▼ 32,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6653,20 +6653,20 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J85" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
@@ -6691,12 +6691,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6721,33 +6721,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 191,00</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 99,0%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>182</v>
+        <v>25</v>
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>▲ 1416,7%</t>
+          <t>▲ 47,1%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6764,12 +6764,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6794,33 +6794,33 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H87" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>▲ 450,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6867,33 +6867,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 96,00</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▼ 32,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6945,20 +6945,20 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J89" s="4" t="inlineStr">
-        <is>
-          <t>▲ 233,3%</t>
+        <v>2</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
@@ -6983,12 +6983,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 96,00</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -7022,29 +7022,29 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>25</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 86,3%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
@@ -7056,78 +7056,516 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>4468602739</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>1854624004</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 33,87</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>182</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1416,7%</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>4468602739</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>1854624004</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 33,87</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>4468602739</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>▲ 233,3%</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>UTD-001-AZ</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>Varal Cabide Azul</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>1854624004</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 33,87</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>4468602739</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>R$ 35,90</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I91" s="2" t="n">
+      <c r="I97" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J91" s="2" t="inlineStr">
+      <c r="J97" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K91" s="2" t="inlineStr">
+      <c r="K97" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="L91" s="2" t="n">
+      <c r="L97" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M91" s="2" t="inlineStr">
+      <c r="M97" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="N91" s="2" t="inlineStr">
+      <c r="N97" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O91" s="2" t="inlineStr">
+      <c r="O97" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O91"/>
+  <autoFilter ref="A1:O97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-001-AZ-VARAL-CABIDE-AZUL.xlsx
+++ b/saida_skus/SKU_UTD-001-AZ-VARAL-CABIDE-AZUL.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O97"/>
+  <dimension ref="A1:O99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 231,00</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>30</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▲ 30,4%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -665,17 +665,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>16</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>▼ 23,8%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>▲ 132,4%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 203,00</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -881,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>▲ 132,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 4,5%</t>
+        <v>0</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -954,33 +954,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
+          <t>R$ 203,00</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,0%</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,14 +997,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -1027,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 102,00</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>▲ 69,2%</t>
+          <t>▼ 4,5%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,14 +1070,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -1100,33 +1100,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>▲ 81,8%</t>
+          <t>▼ 15,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,14 +1143,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -1173,33 +1173,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 169,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>▲ 65,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▼ 7,1%</t>
+          <t>▲ 69,2%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,14 +1216,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -1246,25 +1246,25 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>▲ 10,0%</t>
+        <v>20</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>▲ 81,8%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,14 +1289,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -1319,25 +1319,25 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
+          <t>R$ 169,00</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>▼ 24,4%</t>
+          <t>▲ 65,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 22,2%</t>
+        <v>13</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▼ 7,1%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,14 +1362,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -1392,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>▲ 10,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,14 +1435,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -1465,33 +1465,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 135,00</t>
+          <t>R$ 102,00</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>▲ 32,4%</t>
+          <t>▼ 24,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>14</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▼ 22,2%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,14 +1508,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>▲ 119,4%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>▼ 61,5%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,14 +1581,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -1611,33 +1611,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 135,00</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>▲ 32,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,14 +1654,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -1684,33 +1684,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 31,00</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>▲ 119,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>▲ 62,5%</t>
+          <t>▼ 61,5%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,14 +1727,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -1760,22 +1760,22 @@
           <t>R$ 102,00</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>▲ 50,0%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,14 +1800,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -1833,22 +1833,22 @@
           <t>R$ 31,00</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>▼ 67,0%</t>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>13</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,14 +1873,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -1903,25 +1903,25 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 102,00</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>▲ 45,5%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,14 +1946,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -1976,20 +1976,20 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 94,00</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 31,00</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>▼ 67,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,14 +2019,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -2049,33 +2049,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>▼ 26,7%</t>
+          <t>▲ 45,5%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,14 +2092,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 94,00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>8</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,14 +2165,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -2200,20 +2200,20 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 34,8%</t>
+        <v>11</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▼ 26,7%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,14 +2238,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -2271,17 +2271,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2311,14 +2311,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2350,24 +2350,24 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>▲ 43,8%</t>
+          <t>▼ 34,8%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,14 +2384,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -2414,33 +2414,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 31,00</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 41,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,14 +2457,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -2496,11 +2496,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>▼ 5,9%</t>
+          <t>▲ 43,8%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2530,14 +2530,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -2560,33 +2560,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 31,00</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 7,7%</t>
+        <v>7</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>▼ 41,7%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,14 +2603,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -2636,17 +2636,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 5,6%</t>
+        <v>16</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▼ 5,9%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2676,14 +2676,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -2706,33 +2706,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>12</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>▼ 7,7%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2749,14 +2749,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -2779,33 +2779,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 135,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>▲ 98,5%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>▲ 5,9%</t>
+          <t>▼ 5,6%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2822,14 +2822,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -2852,33 +2852,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 13,3%</t>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2895,14 +2895,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -2925,33 +2925,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 135,00</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>▲ 98,5%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▲ 240,0%</t>
+        <v>18</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2968,14 +2968,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -3003,20 +3003,20 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 28,6%</t>
+        <v>13</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>▼ 13,3%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
@@ -3041,14 +3041,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -3071,33 +3071,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>▼ 58,3%</t>
+          <t>▲ 240,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3114,14 +3114,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -3144,33 +3144,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3187,14 +3187,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -3217,33 +3217,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 7,7%</t>
+        <v>5</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▼ 58,3%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3260,14 +3260,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -3290,33 +3290,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 65,00</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 59,9%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,7%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3333,14 +3333,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -3366,22 +3366,22 @@
           <t>R$ 102,00</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>▲ 18,2%</t>
+          <t>▼ 7,7%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3406,14 +3406,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -3436,33 +3436,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 162,00</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 65,00</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>▼ 59,9%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>▲ 114,3%</t>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,14 +3479,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -3509,33 +3509,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 102,00</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▲ 10,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▲ 18,2%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3552,14 +3552,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -3582,33 +3582,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 162,00</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>15</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▲ 114,3%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3625,14 +3625,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3664,24 +3664,24 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,1%</t>
+          <t>▲ 10,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3698,14 +3698,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -3728,33 +3728,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 67,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
+      <c r="M45" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3771,14 +3771,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -3804,17 +3804,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>▲ 62,5%</t>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3844,14 +3844,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -3874,33 +3874,33 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 97,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>▲ 203,1%</t>
+          <t>▼ 67,0%</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3917,14 +3917,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -3947,33 +3947,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 43,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>▼ 42,9%</t>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3990,14 +3990,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -4020,33 +4020,33 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 97,00</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>▲ 203,1%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>▼ 22,2%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4063,14 +4063,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -4093,33 +4093,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 60,00</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>▼ 43,3%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4136,14 +4136,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -4175,16 +4175,16 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>▼ 22,2%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4209,14 +4209,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -4239,33 +4239,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 180,00</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+          <t>R$ 60,00</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>▲ 31,6%</t>
+          <t>▼ 44,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4282,14 +4282,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -4315,22 +4315,22 @@
           <t>R$ 32,00</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,8%</t>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 9,1%</t>
+        <v>9</v>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
@@ -4355,14 +4355,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -4385,33 +4385,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 210,00</t>
+          <t>R$ 180,00</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>▲ 600,0%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▲ 46,2%</t>
+        <v>25</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▲ 31,6%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4428,14 +4428,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -4458,33 +4458,33 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 65,00</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,8%</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>▼ 8,3%</t>
+        <v>10</v>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4501,14 +4501,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -4531,38 +4531,38 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 30,00</t>
+          <t>R$ 210,00</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>▼ 11,8%</t>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>19</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▲ 46,2%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
@@ -4574,14 +4574,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -4604,33 +4604,33 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 65,00</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>▼ 8,3%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4647,14 +4647,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -4677,16 +4677,16 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 30,00</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>▼ 11,8%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
@@ -4720,14 +4720,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -4750,33 +4750,33 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 65,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>▲ 103,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>12</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4793,14 +4793,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -4828,15 +4828,15 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4866,14 +4866,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -4896,25 +4896,25 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
+          <t>R$ 65,00</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>▲ 103,1%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4939,14 +4939,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -4978,11 +4978,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -4991,11 +4991,11 @@
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5012,14 +5012,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -5042,33 +5042,33 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="inlineStr">
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I63" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>▲ 11,1%</t>
-        </is>
-      </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5085,14 +5085,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -5118,17 +5118,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>15</v>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5158,14 +5158,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -5188,33 +5188,33 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>▼ 30,8%</t>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5231,14 +5231,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -5261,33 +5261,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5304,14 +5304,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -5334,7 +5334,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5343,24 +5343,24 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>▲ 8,3%</t>
+          <t>▼ 30,8%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5377,14 +5377,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -5407,33 +5407,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 102,00</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>▼ 59,8%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 46,7%</t>
+        <v>12</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5450,14 +5450,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -5483,17 +5483,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5523,14 +5523,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -5553,33 +5553,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 169,00</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 9,1%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>▼ 59,8%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 83,4%</t>
+        <v>16</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▼ 46,7%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5596,14 +5596,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -5626,33 +5626,33 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>▲ 5,9%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>▲ 11,1%</t>
+        <v>12</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5669,14 +5669,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -5699,33 +5699,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 186,00</t>
+          <t>R$ 169,00</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>▲ 481,2%</t>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>181</v>
+        <v>30</v>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>▲ 546,4%</t>
+          <t>▼ 83,4%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5742,14 +5742,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -5772,33 +5772,33 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,2%</t>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5815,14 +5815,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -5845,33 +5845,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 186,00</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>▲ 481,2%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 47,4%</t>
+        <v>181</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▲ 546,4%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5888,14 +5888,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -5927,24 +5927,24 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 21,4%</t>
+        <v>9</v>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>▼ 18,2%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5961,14 +5961,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -5991,38 +5991,38 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>28</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▲ 47,4%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
@@ -6034,14 +6034,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -6073,11 +6073,11 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>▲ 7,7%</t>
+          <t>▼ 21,4%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6107,14 +6107,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -6137,38 +6137,38 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,6%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="inlineStr">
+      <c r="M78" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="L78" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="M78" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
@@ -6180,14 +6180,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -6213,17 +6213,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t>▲ 62,5%</t>
+        <v>14</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▲ 7,7%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6253,14 +6253,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -6283,33 +6283,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 129,00</t>
+          <t>R$ 96,00</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>▲ 1,6%</t>
+          <t>▼ 25,6%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,2%</t>
+        <v>0</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6326,14 +6326,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -6356,33 +6356,33 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>▲ 63,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6399,14 +6399,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -6429,33 +6429,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 127,00</t>
-        </is>
-      </c>
-      <c r="H82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 296,9%</t>
+          <t>R$ 129,00</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>▲ 1,6%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 5,9%</t>
+        <v>15</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▼ 6,2%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6472,14 +6472,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -6502,33 +6502,33 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 65,00</t>
-        </is>
-      </c>
-      <c r="H83" s="4" t="inlineStr">
-        <is>
-          <t>▲ 103,1%</t>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>▲ 63,1%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 9,1%</t>
+        <v>8</v>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6545,14 +6545,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -6575,33 +6575,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>R$ 127,00</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>▼ 83,2%</t>
+          <t>▲ 296,9%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 32,0%</t>
+        <v>16</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▼ 5,9%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6618,14 +6618,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -6648,25 +6648,25 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 65,00</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>▲ 103,1%</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>10</v>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -6691,14 +6691,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -6721,33 +6721,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 191,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>▲ 99,0%</t>
+          <t>▼ 83,2%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>▲ 47,1%</t>
+          <t>▼ 32,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6764,12 +6764,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6805,9 +6805,9 @@
       <c r="I87" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="J87" s="4" t="inlineStr">
-        <is>
-          <t>▲ 450,0%</t>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -6837,14 +6837,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -6867,33 +6867,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 191,00</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>▲ 99,0%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>▼ 32,0%</t>
+          <t>▲ 47,1%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6910,14 +6910,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -6949,16 +6949,16 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▲ 450,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
@@ -6983,14 +6983,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -7018,20 +7018,20 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 86,3%</t>
+        <v>17</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>▼ 32,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
@@ -7056,14 +7056,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -7091,20 +7091,20 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
@@ -7112,7 +7112,7 @@
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -7129,14 +7129,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -7159,7 +7159,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 96,00</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -7168,29 +7168,29 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>182</v>
+        <v>25</v>
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>▲ 1416,7%</t>
+          <t>▼ 86,3%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
@@ -7202,14 +7202,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -7232,33 +7232,33 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H93" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7275,14 +7275,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -7314,11 +7314,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>12</v>
+        <v>182</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▲ 1416,7%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7348,14 +7348,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -7378,33 +7378,33 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>▲ 233,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7421,14 +7421,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-001-AZ</t>
@@ -7460,11 +7460,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>12</v>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7494,78 +7494,224 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>4468602739</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>▲ 233,3%</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>UTD-001-AZ</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>Varal Cabide Azul</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>1854624004</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 33,87</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>4468602739</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>R$ 35,90</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I97" s="2" t="n">
+      <c r="I99" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J97" s="2" t="inlineStr">
+      <c r="J99" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K97" s="2" t="inlineStr">
+      <c r="K99" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="L97" s="2" t="n">
+      <c r="L99" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M97" s="2" t="inlineStr">
+      <c r="M99" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="N97" s="2" t="inlineStr">
+      <c r="N99" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O97" s="2" t="inlineStr">
+      <c r="O99" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O97"/>
+  <autoFilter ref="A1:O99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-001-AZ-VARAL-CABIDE-AZUL.xlsx
+++ b/saida_skus/SKU_UTD-001-AZ-VARAL-CABIDE-AZUL.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O99"/>
+  <dimension ref="A1:O103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,29 +589,29 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 231,00</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▲ 30,4%</t>
+        <v>31</v>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3,3%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -665,17 +665,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>▼ 23,8%</t>
+        <v>9</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 30,8%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 255,00</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 10,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 101,00</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>13</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,25 +881,25 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>▲ 132,4%</t>
+          <t>R$ 231,00</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 30,4%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
@@ -907,7 +907,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 203,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -963,24 +963,24 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,8%</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I8" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▼ 4,5%</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1103,17 +1103,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>▼ 15,0%</t>
+        <v>21</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1173,33 +1173,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 237,00</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
+          <t>▲ 132,4%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▲ 69,2%</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,33 +1246,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 203,00</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>▲ 81,8%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1319,33 +1319,33 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 169,00</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>▲ 65,7%</t>
+          <t>R$ 102,00</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▼ 7,1%</t>
+        <v>21</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 4,5%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1392,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>▲ 10,0%</t>
+          <t>▼ 15,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1465,33 +1465,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>▼ 24,4%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>▼ 22,2%</t>
+          <t>▲ 69,2%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>20</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>▲ 81,8%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1611,33 +1611,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 135,00</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>▲ 32,4%</t>
+          <t>R$ 169,00</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>▲ 65,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>13</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,1%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1687,26 +1687,26 @@
           <t>R$ 68,00</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>▲ 119,4%</t>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>▼ 61,5%</t>
+          <t>▲ 10,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1760,22 +1760,22 @@
           <t>R$ 102,00</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 22,2%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1830,33 +1830,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 31,00</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▲ 62,5%</t>
+        <v>10</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1903,20 +1903,20 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 135,00</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 32,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>18</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1925,11 +1925,11 @@
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1976,33 +1976,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 31,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>▼ 67,0%</t>
+          <t>▲ 119,4%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 61,5%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2049,25 +2049,25 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 102,00</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▲ 45,5%</t>
+        <v>18</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2122,25 +2122,25 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 94,00</t>
+          <t>R$ 31,00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2195,33 +2195,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 102,00</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▼ 26,7%</t>
+        <v>12</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2268,33 +2268,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 31,00</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 67,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2341,33 +2341,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>▼ 34,8%</t>
+          <t>▲ 45,5%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2414,33 +2414,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 94,00</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2487,33 +2487,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>▲ 43,8%</t>
+          <t>▼ 26,7%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 31,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2569,24 +2569,24 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>▼ 41,7%</t>
+        <v>2</v>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2642,24 +2642,24 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▼ 5,9%</t>
+        <v>15</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 34,8%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2709,17 +2709,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>▼ 7,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2782,17 +2782,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>▼ 5,6%</t>
+          <t>▲ 43,8%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2852,33 +2852,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 31,00</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>7</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 41,7%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2895,12 +2895,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2925,33 +2925,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 135,00</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>▲ 98,5%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>▲ 5,9%</t>
+          <t>▼ 5,9%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2968,12 +2968,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2998,33 +2998,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>▼ 13,3%</t>
+        <v>12</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,7%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
@@ -3084,20 +3084,20 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>▲ 240,0%</t>
+          <t>▼ 5,6%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3114,12 +3114,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3144,33 +3144,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>▼ 28,6%</t>
+        <v>13</v>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3217,33 +3217,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 135,00</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 98,5%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>▼ 58,3%</t>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3290,33 +3290,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 13,3%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3333,12 +3333,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3363,33 +3363,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>▼ 7,7%</t>
+          <t>▲ 240,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3436,25 +3436,25 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 65,00</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>▼ 59,9%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>▼ 6,7%</t>
+        <v>15</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3509,33 +3509,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>▲ 18,2%</t>
+          <t>▼ 58,3%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3582,33 +3582,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 162,00</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▲ 114,3%</t>
+        <v>21</v>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3655,33 +3655,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 102,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>▲ 10,0%</t>
+          <t>▼ 7,7%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3728,33 +3728,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H45" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 65,00</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 59,9%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>14</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3801,33 +3801,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 102,00</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>▼ 23,1%</t>
+          <t>▲ 18,2%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3874,33 +3874,33 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H47" s="4" t="inlineStr">
-        <is>
-          <t>▼ 67,0%</t>
+          <t>R$ 162,00</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 114,3%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3947,33 +3947,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▲ 62,5%</t>
+        <v>11</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>▲ 10,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3990,12 +3990,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4020,33 +4020,33 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 97,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>▲ 203,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4063,12 +4063,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4093,33 +4093,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>▼ 43,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+        <v>10</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4169,22 +4169,22 @@
           <t>R$ 32,00</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 67,0%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>▼ 22,2%</t>
+        <v>0</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4239,33 +4239,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 60,00</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>▼ 44,0%</t>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4312,33 +4312,33 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 97,00</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>▲ 203,1%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>▼ 10,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4385,33 +4385,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 180,00</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 43,3%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>▲ 31,6%</t>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4461,22 +4461,22 @@
           <t>R$ 32,00</t>
         </is>
       </c>
-      <c r="H55" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,8%</t>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>▼ 9,1%</t>
+        <v>7</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>▼ 22,2%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4531,33 +4531,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 210,00</t>
+          <t>R$ 60,00</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>▲ 600,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>▲ 46,2%</t>
+          <t>▼ 44,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4574,12 +4574,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4604,33 +4604,33 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 65,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>▼ 8,3%</t>
+        <v>9</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4677,38 +4677,38 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 30,00</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>▼ 11,8%</t>
+          <t>R$ 180,00</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>25</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▲ 31,6%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
@@ -4720,12 +4720,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4750,33 +4750,33 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H59" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,8%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4793,12 +4793,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4823,33 +4823,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 210,00</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>19</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>▲ 46,2%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4899,30 +4899,30 @@
           <t>R$ 65,00</t>
         </is>
       </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>▲ 103,1%</t>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>11</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,3%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4969,25 +4969,25 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
+          <t>R$ 30,00</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,8%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
@@ -4995,12 +4995,12 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
@@ -5012,12 +5012,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5042,33 +5042,33 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
+      <c r="M63" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M63" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5115,33 +5115,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I64" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5188,33 +5188,33 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 65,00</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 103,1%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▲ 11,1%</t>
+        <v>15</v>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5261,18 +5261,18 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J66" s="4" t="inlineStr">
+      <c r="J66" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -5283,11 +5283,11 @@
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5304,12 +5304,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5343,16 +5343,16 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t>▼ 30,8%</t>
+        <v>0</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5377,12 +5377,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5407,33 +5407,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>15</v>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5450,12 +5450,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5483,17 +5483,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>▲ 8,3%</t>
+        <v>10</v>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5553,33 +5553,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>▼ 59,8%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▼ 46,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5626,33 +5626,33 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H71" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>▲ 20,0%</t>
+          <t>▼ 30,8%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5699,33 +5699,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 169,00</t>
+          <t>R$ 102,00</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>▼ 9,1%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▼ 83,4%</t>
+        <v>12</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5742,12 +5742,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5772,33 +5772,33 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>▲ 5,9%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▲ 11,1%</t>
+        <v>13</v>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5845,33 +5845,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 186,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>▲ 481,2%</t>
+          <t>▼ 59,8%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>181</v>
+        <v>16</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>▲ 546,4%</t>
+          <t>▼ 46,7%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5918,33 +5918,33 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>▼ 18,2%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5961,12 +5961,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5991,33 +5991,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 169,00</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>▲ 47,4%</t>
+          <t>▼ 83,4%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6064,33 +6064,33 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>▼ 21,4%</t>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6107,12 +6107,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6137,38 +6137,38 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 186,00</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 481,2%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>181</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 546,4%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6219,24 +6219,24 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>▲ 7,7%</t>
+          <t>▼ 18,2%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6253,12 +6253,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6283,33 +6283,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
-        </is>
-      </c>
-      <c r="H80" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,6%</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 47,4%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6326,12 +6326,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6359,17 +6359,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H81" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>▲ 62,5%</t>
+          <t>▼ 21,4%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6399,12 +6399,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6429,38 +6429,38 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 129,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>▲ 1,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▼ 6,2%</t>
+        <v>19</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6502,33 +6502,33 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
-        </is>
-      </c>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t>▲ 63,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▲ 7,7%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6545,12 +6545,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6575,33 +6575,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 127,00</t>
+          <t>R$ 96,00</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>▲ 296,9%</t>
+          <t>▼ 25,6%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>▼ 5,9%</t>
+        <v>0</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6648,33 +6648,33 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 65,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>▲ 103,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>▼ 9,1%</t>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -6691,12 +6691,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6721,33 +6721,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>R$ 129,00</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>▼ 83,2%</t>
+          <t>▲ 1,6%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>▼ 32,0%</t>
+        <v>15</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,2%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6764,12 +6764,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6794,33 +6794,33 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>▲ 63,1%</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>8</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6867,33 +6867,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 191,00</t>
-        </is>
-      </c>
-      <c r="H88" s="3" t="inlineStr">
-        <is>
-          <t>▲ 99,0%</t>
+          <t>R$ 127,00</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>▲ 296,9%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>▲ 47,1%</t>
+          <t>▼ 5,9%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6940,25 +6940,25 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 65,00</t>
+        </is>
+      </c>
+      <c r="H89" s="4" t="inlineStr">
+        <is>
+          <t>▲ 103,1%</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>▲ 450,0%</t>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7013,33 +7013,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 83,2%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="J90" s="4" t="inlineStr">
+      <c r="J90" s="3" t="inlineStr">
         <is>
           <t>▼ 32,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7056,12 +7056,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7095,16 +7095,16 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J91" s="4" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
@@ -7112,7 +7112,7 @@
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -7129,12 +7129,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 191,00</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>▲ 99,0%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
@@ -7172,25 +7172,25 @@
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>▼ 86,3%</t>
+          <t>▲ 47,1%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
@@ -7202,12 +7202,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7237,20 +7237,20 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J93" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>▲ 450,0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7305,33 +7305,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 96,00</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>182</v>
+        <v>17</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>▲ 1416,7%</t>
+          <t>▼ 32,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7378,33 +7378,33 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H95" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J95" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 96,00</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -7460,29 +7460,29 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J96" s="4" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>25</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 86,3%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
@@ -7494,12 +7494,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7535,9 +7535,9 @@
       <c r="I97" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>▲ 233,3%</t>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -7567,12 +7567,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7606,11 +7606,11 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>182</v>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1416,7%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7673,17 +7673,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7710,8 +7710,300 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>1854624004</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 33,87</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>4468602739</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>▲ 233,3%</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>1854624004</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 33,87</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>4468602739</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O99"/>
+  <autoFilter ref="A1:O103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-001-AZ-VARAL-CABIDE-AZUL.xlsx
+++ b/saida_skus/SKU_UTD-001-AZ-VARAL-CABIDE-AZUL.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O103"/>
+  <dimension ref="A1:O127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 223,00</t>
+          <t>R$ 66,00</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>▼ 12,5%</t>
+          <t>▼ 78,4%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3,3%</t>
+        <v>23</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 32,4%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 66,3%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 30,8%</t>
+        <v>12</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 255,00</t>
+          <t>R$ 305,00</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>▲ 10,4%</t>
+          <t>▲ 348,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>34</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,1%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -817,24 +817,24 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,8%</t>
+          <t>▼ 52,9%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 231,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -890,24 +890,24 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>▲ 30,4%</t>
+          <t>▲ 60,9%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -963,11 +963,11 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▼ 23,8%</t>
+        <v>17</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>▲ 21,4%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1038,9 +1038,9 @@
       <c r="I8" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 43,9%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1109,11 +1109,11 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>14</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1173,33 +1173,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 237,00</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>▲ 132,4%</t>
+          <t>R$ 102,00</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 24,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 10,9%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,33 +1246,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 203,00</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>15</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1319,25 +1319,25 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 135,00</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>▼ 4,5%</t>
+          <t>▼ 27,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1392,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1465,33 +1465,33 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 339,00</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 43,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>▲ 69,2%</t>
+          <t>▲ 5,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>▲ 81,8%</t>
+        <v>10</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 58,3%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1611,33 +1611,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 169,00</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>▲ 65,7%</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 7,1%</t>
+        <v>60</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▲ 7,1%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1693,16 +1693,16 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>▲ 10,0%</t>
+          <t>▲ 4,3%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1757,33 +1757,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>▼ 24,4%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 22,2%</t>
+        <v>56</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>▲ 19,1%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1839,11 +1839,11 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 109,1%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1903,33 +1903,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 135,00</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 32,4%</t>
+          <t>R$ 64,00</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>47</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 88,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1976,33 +1976,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>▲ 119,4%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 74,8%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>▼ 61,5%</t>
+          <t>▼ 8,3%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2049,33 +2049,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 96,00</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 62,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 4,2%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2122,33 +2122,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 31,00</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 135,00</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>▲ 62,5%</t>
+        <v>12</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2195,33 +2195,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
+          <t>R$ 255,00</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 22,6%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2268,33 +2268,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 31,00</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 67,0%</t>
+          <t>R$ 101,00</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>15</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2341,33 +2341,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 223,00</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 12,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>▲ 45,5%</t>
+          <t>▲ 3,3%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2414,33 +2414,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 94,00</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 30,8%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2487,33 +2487,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
+          <t>R$ 255,00</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 10,4%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 26,7%</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 101,00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2569,24 +2569,24 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>13</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,8%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 231,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2642,24 +2642,24 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 34,8%</t>
+        <v>30</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 30,4%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2709,17 +2709,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 23,8%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2782,17 +2782,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 43,8%</t>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2852,33 +2852,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 31,00</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 41,7%</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2895,12 +2895,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2925,20 +2925,20 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 237,00</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 132,4%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>▼ 5,9%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2947,11 +2947,11 @@
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2968,12 +2968,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2998,33 +2998,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
+          <t>R$ 203,00</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I35" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 7,7%</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3071,33 +3071,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 102,00</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>▼ 5,6%</t>
+          <t>▼ 4,5%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3114,12 +3114,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3144,33 +3144,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>17</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3217,33 +3217,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 135,00</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>▲ 98,5%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>▲ 5,9%</t>
+          <t>▲ 69,2%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3290,25 +3290,25 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 13,3%</t>
+        <v>20</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>▲ 81,8%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3333,12 +3333,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3363,25 +3363,25 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 169,00</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>▲ 65,7%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>▲ 240,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,1%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3445,16 +3445,16 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 28,6%</t>
+        <v>11</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>▲ 10,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3509,33 +3509,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 102,00</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 24,4%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>▼ 58,3%</t>
+          <t>▼ 22,2%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3552,12 +3552,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3591,11 +3591,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3655,25 +3655,25 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
+          <t>R$ 135,00</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>▲ 32,4%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I44" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 7,7%</t>
-        </is>
-      </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3728,33 +3728,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 65,00</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 59,9%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>▲ 119,4%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,7%</t>
+          <t>▼ 61,5%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3804,30 +3804,30 @@
           <t>R$ 102,00</t>
         </is>
       </c>
-      <c r="H46" s="4" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
         <is>
           <t>▲ 50,0%</t>
         </is>
       </c>
-      <c r="I46" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▲ 18,2%</t>
-        </is>
-      </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3874,33 +3874,33 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 162,00</t>
+          <t>R$ 31,00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>▲ 114,3%</t>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3947,25 +3947,25 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 102,00</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>▲ 10,0%</t>
+        <v>12</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3990,12 +3990,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4020,33 +4020,33 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 31,00</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 67,0%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4063,12 +4063,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4093,33 +4093,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 23,1%</t>
+        <v>16</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▲ 45,5%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4166,25 +4166,25 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 67,0%</t>
+          <t>R$ 94,00</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4239,33 +4239,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>▲ 62,5%</t>
+        <v>11</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 26,7%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4312,33 +4312,33 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 97,00</t>
-        </is>
-      </c>
-      <c r="H53" s="4" t="inlineStr">
-        <is>
-          <t>▲ 203,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4388,22 +4388,22 @@
           <t>R$ 34,00</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 43,3%</t>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>▼ 42,9%</t>
+          <t>▼ 34,8%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
@@ -4428,12 +4428,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4458,33 +4458,33 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>▼ 22,2%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4531,33 +4531,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 60,00</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,0%</t>
+        <v>23</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>▲ 43,8%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4574,12 +4574,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4604,25 +4604,25 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>R$ 31,00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>▼ 10,0%</t>
+          <t>▼ 41,7%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4677,33 +4677,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 180,00</t>
-        </is>
-      </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 31,6%</t>
+        <v>16</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,9%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4720,12 +4720,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4750,33 +4750,33 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,8%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>▼ 9,1%</t>
+          <t>▼ 7,7%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4793,12 +4793,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4823,33 +4823,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 210,00</t>
-        </is>
-      </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>▲ 46,2%</t>
+        <v>17</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,6%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4896,33 +4896,33 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 65,00</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 8,3%</t>
+        <v>13</v>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4969,38 +4969,38 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 30,00</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 11,8%</t>
+          <t>R$ 135,00</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 98,5%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>18</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
@@ -5012,12 +5012,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5042,33 +5042,33 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 13,3%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5115,33 +5115,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>17</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 240,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5188,20 +5188,20 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 65,00</t>
-        </is>
-      </c>
-      <c r="H65" s="4" t="inlineStr">
-        <is>
-          <t>▲ 103,1%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 28,6%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5261,33 +5261,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 58,3%</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr">
+      <c r="M66" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M66" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5304,12 +5304,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5334,33 +5334,33 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K67" s="2" t="inlineStr">
+      <c r="M67" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M67" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5377,12 +5377,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5407,33 +5407,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 102,00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>12</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,7%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5450,12 +5450,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5480,33 +5480,33 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 65,00</t>
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 59,9%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>▲ 11,1%</t>
+        <v>14</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5553,33 +5553,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 102,00</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 18,2%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>R$ 162,00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5635,24 +5635,24 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 30,8%</t>
+        <v>15</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>▲ 114,3%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5699,33 +5699,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 102,00</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 10,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5742,12 +5742,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5775,17 +5775,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
         <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5845,33 +5845,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 59,8%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>▼ 46,7%</t>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5918,33 +5918,33 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
+          <t>▼ 67,0%</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I75" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
-        </is>
-      </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5961,12 +5961,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5991,33 +5991,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 169,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>▼ 9,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 83,4%</t>
+        <v>13</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6064,33 +6064,33 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
+          <t>R$ 97,00</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>▲ 5,9%</t>
+          <t>▲ 203,1%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>▲ 11,1%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6107,12 +6107,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6137,33 +6137,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 186,00</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 481,2%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 43,3%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>181</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 546,4%</t>
+        <v>8</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6210,33 +6210,33 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>▼ 18,2%</t>
+          <t>▼ 22,2%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6253,12 +6253,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6283,33 +6283,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 60,00</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 47,4%</t>
+        <v>14</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6326,12 +6326,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6356,33 +6356,33 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>▼ 21,4%</t>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6399,12 +6399,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6429,38 +6429,38 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 180,00</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>25</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 31,6%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6502,33 +6502,33 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,8%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J83" s="4" t="inlineStr">
-        <is>
-          <t>▲ 7,7%</t>
+        <v>10</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6545,12 +6545,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6575,33 +6575,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,6%</t>
+          <t>R$ 210,00</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>19</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 46,2%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6648,33 +6648,33 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 65,00</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J85" s="4" t="inlineStr">
-        <is>
-          <t>▲ 62,5%</t>
+        <v>11</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 8,3%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -6691,12 +6691,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6721,38 +6721,38 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 129,00</t>
-        </is>
-      </c>
-      <c r="H86" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1,6%</t>
+          <t>R$ 30,00</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 11,8%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,2%</t>
+        <v>13</v>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
@@ -6764,12 +6764,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6794,16 +6794,16 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 106,00</t>
-        </is>
-      </c>
-      <c r="H87" s="4" t="inlineStr">
-        <is>
-          <t>▲ 63,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
@@ -6812,15 +6812,15 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6867,33 +6867,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 127,00</t>
-        </is>
-      </c>
-      <c r="H88" s="4" t="inlineStr">
-        <is>
-          <t>▲ 296,9%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 5,9%</t>
+        <v>0</v>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6949,16 +6949,16 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 9,1%</t>
+        <v>15</v>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7013,25 +7013,25 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 83,2%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>▼ 32,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7056,12 +7056,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7091,20 +7091,20 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
@@ -7112,7 +7112,7 @@
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -7129,12 +7129,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7159,33 +7159,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 191,00</t>
-        </is>
-      </c>
-      <c r="H92" s="4" t="inlineStr">
-        <is>
-          <t>▲ 99,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>▲ 47,1%</t>
+        <v>15</v>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7202,12 +7202,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7232,33 +7232,33 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>▲ 450,0%</t>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7305,33 +7305,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>▼ 32,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7383,20 +7383,20 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▼ 30,8%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7451,38 +7451,38 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 96,00</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 102,00</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>▼ 86,3%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
@@ -7494,12 +7494,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7524,7 +7524,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7533,24 +7533,24 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L97" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -7567,12 +7567,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7597,33 +7597,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 59,8%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>182</v>
-      </c>
-      <c r="J98" s="4" t="inlineStr">
-        <is>
-          <t>▲ 1416,7%</t>
+        <v>16</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 46,7%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7679,11 +7679,11 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J99" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>12</v>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7743,33 +7743,33 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 169,00</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▼ 83,4%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7816,12 +7816,12 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>▲ 233,3%</t>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -7859,12 +7859,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7889,33 +7889,33 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 186,00</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>▲ 481,2%</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>181</v>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>▲ 546,4%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -7932,78 +7932,1830 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>4468602739</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>▼ 18,2%</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>22,2%</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>1854624004</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 33,87</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>▲ 47,4%</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>4468602739</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,4%</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>1854624004</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 33,87</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>4468602739</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>▲ 7,7%</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>1854624004</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 33,87</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 96,00</t>
+        </is>
+      </c>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,6%</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>4468602739</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H109" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>▲ 62,5%</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>1854624004</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 33,87</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 129,00</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1,6%</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,2%</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>26,7%</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>4468602739</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>R$ 106,00</t>
+        </is>
+      </c>
+      <c r="H111" s="4" t="inlineStr">
+        <is>
+          <t>▲ 63,1%</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>1854624004</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 33,87</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 127,00</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t>▲ 296,9%</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 5,9%</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>18,8%</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>4468602739</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>R$ 65,00</t>
+        </is>
+      </c>
+      <c r="H113" s="4" t="inlineStr">
+        <is>
+          <t>▲ 103,1%</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>1854624004</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 33,87</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 83,2%</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 32,0%</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>5,9%</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>4468602739</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>1854624004</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 33,87</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 191,00</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>▲ 99,0%</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>▲ 47,1%</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>4468602739</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t>▲ 450,0%</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>1854624004</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 33,87</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 96,00</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 32,0%</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>17,6%</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>4468602739</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>1854624004</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 33,87</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 96,00</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 86,3%</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>12,0%</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>4468602739</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J121" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>1854624004</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 33,87</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>182</v>
+      </c>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>▲ 1416,7%</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>4468602739</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H123" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>1854624004</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 33,87</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>4468602739</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J125" s="4" t="inlineStr">
+        <is>
+          <t>▲ 233,3%</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>UTD-001-AZ</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>Varal Cabide Azul</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>1854624004</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 33,87</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>UTD-001-AZ</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Varal Cabide Azul</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>4468602739</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>R$ 35,90</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I103" s="2" t="n">
+      <c r="I127" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J103" s="2" t="inlineStr">
+      <c r="J127" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K103" s="2" t="inlineStr">
+      <c r="K127" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="L103" s="2" t="n">
+      <c r="L127" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M103" s="2" t="inlineStr">
+      <c r="M127" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="N103" s="2" t="inlineStr">
+      <c r="N127" s="2" t="inlineStr">
         <is>
           <t>Sem calcular</t>
         </is>
       </c>
-      <c r="O103" s="2" t="inlineStr">
+      <c r="O127" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O103"/>
+  <autoFilter ref="A1:O127"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>